--- a/Production/MOTBoard_780/MOT780_Board.xlsx
+++ b/Production/MOTBoard_780/MOT780_Board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Augenblick/Documents/2025Summer/FreeCAD/Boards/PyOpticL_Rubidium_System/Production/MOTBoard_780/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68813FD6-2056-CF49-9CE6-8F77BFEBB2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBDB076-5BE8-104F-BFAF-D91B07218570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-64660" yWindow="-280" windowWidth="28040" windowHeight="17440" xr2:uid="{42F6A15E-87CE-9147-9545-45C46C70D310}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" xr2:uid="{42F6A15E-87CE-9147-9545-45C46C70D310}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -520,7 +520,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
